--- a/KatalonData/RADTestData/TaxPayerSSNNoMatch.xlsx
+++ b/KatalonData/RADTestData/TaxPayerSSNNoMatch.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t465179\Documents\git\VPS-Katalon\VPS-Katalon\KatalonData\RADTestData\"/>
     </mc:Choice>
@@ -17,7 +17,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="25">
   <si>
     <t>Result</t>
   </si>
@@ -94,12 +94,28 @@
   </si>
   <si>
     <t>Wed Aug 05 11:49:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:41:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:41:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:42:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:43:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:43:55 IST 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -469,12 +485,12 @@
   <dimension ref="A1:E7"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="7.46484375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="26.46484375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="15.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="34.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="7.46484375" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.46484375" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="15.46484375" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="34.46484375" collapsed="true"/>
+    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.45">
@@ -499,7 +515,7 @@
         <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>4</v>
@@ -516,7 +532,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>4</v>
@@ -533,7 +549,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>4</v>
@@ -550,7 +566,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>4</v>
@@ -584,7 +600,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>4</v>

--- a/KatalonData/RADTestData/TaxPayerSSNNoMatch.xlsx
+++ b/KatalonData/RADTestData/TaxPayerSSNNoMatch.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t465179\Documents\git\VPS-Katalon\VPS-Katalon\KatalonData\RADTestData\"/>
     </mc:Choice>
@@ -17,7 +17,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="25">
   <si>
     <t>Result</t>
   </si>
@@ -94,12 +94,28 @@
   </si>
   <si>
     <t>Wed Aug 05 11:49:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:16:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:16:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:16:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:16:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:16:52 EDT 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -469,12 +485,12 @@
   <dimension ref="A1:E7"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="7.46484375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="26.46484375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="15.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="34.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="7.46484375" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.46484375" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="15.46484375" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="34.46484375" collapsed="true"/>
+    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.45">
@@ -499,7 +515,7 @@
         <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>4</v>
@@ -516,7 +532,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>4</v>
@@ -533,7 +549,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>4</v>
@@ -550,7 +566,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>4</v>
@@ -584,7 +600,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>4</v>
